--- a/Treinamento/IndexacaoFG/Arquivos/BLOQUEIOS HONDA 01.12.2025.xlsx
+++ b/Treinamento/IndexacaoFG/Arquivos/BLOQUEIOS HONDA 01.12.2025.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="19" documentId="8_{2C199E82-2198-4688-8630-9ED385D9F712}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CEC31AE2-F0BA-412F-B2E0-A3879BB22334}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{49E03E13-C02B-453A-87EF-14C60E074F4A}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{49E03E13-C02B-453A-87EF-14C60E074F4A}"/>
   </bookViews>
   <sheets>
     <sheet name="Bloqueios 01.12.2025" sheetId="1" r:id="rId1"/>
@@ -1286,6 +1286,49 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <DossierOwner xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea">
+      <UserInfo>
+        <DisplayName/>
+        <AccountId xsi:nil="true"/>
+        <AccountType/>
+      </UserInfo>
+    </DossierOwner>
+    <_ip_UnifiedCompliancePolicyUIAction xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+    <ccca9d190a3c43e89f73773ee806c8b5 xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </ccca9d190a3c43e89f73773ee806c8b5>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="ea6c6725-5210-4d6a-93cc-4cf85111ac5e">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <ContractDate xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" xsi:nil="true"/>
+    <MailPreviewData xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" xsi:nil="true"/>
+    <_Flow_SignoffStatus xmlns="ea6c6725-5210-4d6a-93cc-4cf85111ac5e" xsi:nil="true"/>
+    <_ip_UnifiedCompliancePolicyProperties xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+    <ContractExpirationDate xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" xsi:nil="true"/>
+    <DossierStatus xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" xsi:nil="true"/>
+    <ia4b831ccad64069ad2e0cbd870e9b8a xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </ia4b831ccad64069ad2e0cbd870e9b8a>
+    <TaxCatchAll xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" xsi:nil="true"/>
+    <alteradopor xmlns="ea6c6725-5210-4d6a-93cc-4cf85111ac5e">
+      <UserInfo>
+        <DisplayName/>
+        <AccountId xsi:nil="true"/>
+        <AccountType/>
+      </UserInfo>
+    </alteradopor>
+    <_dlc_DocId xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea">QAFFA7D2F2TC-2102087286-530989</_dlc_DocId>
+    <_dlc_DocIdUrl xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea">
+      <Url>https://allianzms.sharepoint.com/teams/BR0010-4356589/_layouts/15/DocIdRedir.aspx?ID=QAFFA7D2F2TC-2102087286-530989</Url>
+      <Description>QAFFA7D2F2TC-2102087286-530989</Description>
+    </_dlc_DocIdUrl>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010006E7B04763359F4AAB0FC84D5027BFC8" ma:contentTypeVersion="44" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="522e863aef51f288a2c445becadad51a">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns1="http://schemas.microsoft.com/sharepoint/v3" xmlns:ns2="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" xmlns:ns3="ea6c6725-5210-4d6a-93cc-4cf85111ac5e" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="e2cd90bc508d2ca63574b1ae88af87c9" ns1:_="" ns2:_="" ns3:_="">
     <xsd:import namespace="http://schemas.microsoft.com/sharepoint/v3"/>
@@ -1663,59 +1706,7 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <DossierOwner xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea">
-      <UserInfo>
-        <DisplayName/>
-        <AccountId xsi:nil="true"/>
-        <AccountType/>
-      </UserInfo>
-    </DossierOwner>
-    <_ip_UnifiedCompliancePolicyUIAction xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <ccca9d190a3c43e89f73773ee806c8b5 xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </ccca9d190a3c43e89f73773ee806c8b5>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="ea6c6725-5210-4d6a-93cc-4cf85111ac5e">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <ContractDate xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" xsi:nil="true"/>
-    <MailPreviewData xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" xsi:nil="true"/>
-    <_Flow_SignoffStatus xmlns="ea6c6725-5210-4d6a-93cc-4cf85111ac5e" xsi:nil="true"/>
-    <_ip_UnifiedCompliancePolicyProperties xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <ContractExpirationDate xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" xsi:nil="true"/>
-    <DossierStatus xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" xsi:nil="true"/>
-    <ia4b831ccad64069ad2e0cbd870e9b8a xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </ia4b831ccad64069ad2e0cbd870e9b8a>
-    <TaxCatchAll xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" xsi:nil="true"/>
-    <alteradopor xmlns="ea6c6725-5210-4d6a-93cc-4cf85111ac5e">
-      <UserInfo>
-        <DisplayName/>
-        <AccountId xsi:nil="true"/>
-        <AccountType/>
-      </UserInfo>
-    </alteradopor>
-    <_dlc_DocId xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea">QAFFA7D2F2TC-2102087286-530989</_dlc_DocId>
-    <_dlc_DocIdUrl xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea">
-      <Url>https://allianzms.sharepoint.com/teams/BR0010-4356589/_layouts/15/DocIdRedir.aspx?ID=QAFFA7D2F2TC-2102087286-530989</Url>
-      <Description>QAFFA7D2F2TC-2102087286-530989</Description>
-    </_dlc_DocIdUrl>
-  </documentManagement>
-</p:properties>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <spe:Receivers xmlns:spe="http://schemas.microsoft.com/sharepoint/events">
   <Receiver>
@@ -1765,7 +1756,28 @@
 </spe:Receivers>
 </file>
 
+<file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{809F9E28-94E1-4EB1-B9AC-67B6780BD594}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
+    <ds:schemaRef ds:uri="ea6c6725-5210-4d6a-93cc-4cf85111ac5e"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{17D93DE9-4CF8-455D-8AD4-321D96897313}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -1785,30 +1797,18 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{809F9E28-94E1-4EB1-B9AC-67B6780BD594}">
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{34A3AA62-C449-41FA-A4AD-BF0DD43A488A}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
-    <ds:schemaRef ds:uri="ea6c6725-5210-4d6a-93cc-4cf85111ac5e"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/events"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C4A950BF-0CCB-46D6-B668-33E6B9F8FDC0}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{34A3AA62-C449-41FA-A4AD-BF0DD43A488A}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/events"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>